--- a/docs/report/gantt-chart.xlsx
+++ b/docs/report/gantt-chart.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd.mm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +65,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="0052514E"/>
     </font>
   </fonts>
   <fills count="10">
@@ -179,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -235,7 +230,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,7 +354,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Claude</author>
+    <author>Cerio</author>
   </authors>
   <commentList>
     <comment ref="F5" authorId="0" shapeId="0">
@@ -1458,28 +1452,23 @@
           <t>Game engine</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Plan drafted with Claude, 07.10.2026</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Levels</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>Bot</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Graphics</t>
         </is>
